--- a/output/pdf_financials_xlsx/SM.xlsx
+++ b/output/pdf_financials_xlsx/SM.xlsx
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.221368</v>
+        <v>-0.221368</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.20347</v>
+        <v>-1.20347</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>7.112179</v>
+        <v>-7.112179</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>3.976253</v>
@@ -987,19 +987,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.221368</v>
+        <v>-0.221368</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.20347</v>
+        <v>-1.20347</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>7.112179</v>
+        <v>-7.112179</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.562744</v>
+        <v>-2.562744</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>39.99905</v>
+        <v>-39.99905</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-4.075728</v>
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.221368</v>
+        <v>-0.221368</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.20347</v>
+        <v>-1.20347</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>7.112179</v>
+        <v>-7.112179</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.562744</v>
+        <v>-2.562744</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>39.99905</v>
+        <v>-39.99905</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-4.075728</v>
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>11.0684</v>
+        <v>-11.0684</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>24.0694</v>
+        <v>-24.0694</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>54.709069</v>
+        <v>-54.709069</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>64.0686</v>
+        <v>-64.0686</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>124.997031</v>
+        <v>-124.997031</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>135.8576</v>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.221368</v>
+        <v>-0.221368</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.20347</v>
+        <v>-1.20347</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>7.112179</v>
+        <v>-7.112179</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>3.976253</v>
@@ -1239,13 +1239,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.221368</v>
+        <v>-0.221368</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.20347</v>
+        <v>-1.20347</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>7.114475</v>
+        <v>-7.109883</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>3.989957</v>
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>35.54876915528262</v>
@@ -18758,10 +18758,10 @@
         </is>
       </c>
       <c r="I283" s="5" t="n">
-        <v>39.99905</v>
+        <v>-39.99905</v>
       </c>
       <c r="J283" s="5" t="n">
-        <v>4.075728</v>
+        <v>-4.075728</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -18860,10 +18860,10 @@
         </is>
       </c>
       <c r="I285" s="5" t="n">
-        <v>39.848263</v>
+        <v>-39.848263</v>
       </c>
       <c r="J285" s="5" t="n">
-        <v>4.42037</v>
+        <v>-4.42037</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -19871,10 +19871,10 @@
         </is>
       </c>
       <c r="H305" s="5" t="n">
-        <v>2.562744</v>
+        <v>-2.562744</v>
       </c>
       <c r="I305" s="5" t="n">
-        <v>39.99905</v>
+        <v>-39.99905</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
@@ -19975,10 +19975,10 @@
         </is>
       </c>
       <c r="H307" s="5" t="n">
-        <v>2.562744</v>
+        <v>-2.562744</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>39.848263</v>
+        <v>-39.848263</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -20807,16 +20807,16 @@
         </is>
       </c>
       <c r="E324" s="5" t="n">
-        <v>0.221368</v>
+        <v>-0.221368</v>
       </c>
       <c r="F324" s="5" t="n">
-        <v>1.20347</v>
+        <v>-1.20347</v>
       </c>
       <c r="G324" s="5" t="n">
-        <v>7.112179</v>
+        <v>-7.112179</v>
       </c>
       <c r="H324" s="5" t="n">
-        <v>8.246715</v>
+        <v>-8.246715</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SM.xlsx
+++ b/output/pdf_financials_xlsx/SM.xlsx
@@ -738,13 +738,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002301</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008819</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.051534</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>-0.101305</v>
@@ -1186,13 +1186,13 @@
         <v>-0.221368</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.20347</v>
+        <v>-1.201169</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.112179</v>
+        <v>-7.10336</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.976253</v>
+        <v>4.027787</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>39.85363</v>
@@ -1242,13 +1242,13 @@
         <v>-0.221368</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.20347</v>
+        <v>-1.201169</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.109883</v>
+        <v>-7.101064</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.989957</v>
+        <v>4.041491</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>39.864585</v>
@@ -4180,16 +4180,16 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.016266</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.00831</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.007485</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008324</v>
       </c>
     </row>
     <row r="125">
@@ -4208,16 +4208,16 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.016266</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.00831</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.007485</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008324</v>
       </c>
     </row>
     <row r="126">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -11606,7 +11606,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -17164,7 +17168,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -18303,7 +18307,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -20309,7 +20313,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">

--- a/output/pdf_financials_xlsx/SM.xlsx
+++ b/output/pdf_financials_xlsx/SM.xlsx
@@ -599,10 +599,10 @@
         <v>0.267</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.401813</v>
+        <v>0.482813</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.996673</v>
+        <v>1.104673</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -683,7 +683,7 @@
         <v>0.412424</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.587842</v>
+        <v>0.668842</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>2.964007</v>
@@ -711,7 +711,7 @@
         <v>-0.412424</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.587842</v>
+        <v>-0.668842</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-2.964007</v>
@@ -3811,10 +3811,10 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007655</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.071101</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -4471,10 +4471,10 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007655</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.071101</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -4501,10 +4501,10 @@
         <v>-1.334181</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-4.699812</v>
+        <v>-4.707467</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-10.484883</v>
+        <v>-10.555984</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-5.098982</v>
@@ -11300,7 +11300,11 @@
           <t>Shares issued for cash (Note 13)</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -12349,7 +12353,11 @@
           <t>Deferred income tax expense (Note 12)</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -12804,7 +12812,11 @@
           <t>Shares issued for cash (Note 15)</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -13408,7 +13420,11 @@
           <t>Deferred income tax expense (recovery) (Note 11)</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -13708,7 +13724,11 @@
           <t>Shares issued for cash (Note 14)</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -14206,7 +14226,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -14304,7 +14328,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -17423,7 +17451,11 @@
           <t>Deferred income tax recovery (expense) (Note 11)</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -20213,7 +20245,11 @@
           <t>Director fees (Note 6)</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
